--- a/docs/tx_assumptions.xlsx
+++ b/docs/tx_assumptions.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1097,958 +1097,871 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B4" t="n">
-        <v>2790.6147</v>
+        <v>2454.7594</v>
       </c>
       <c r="C4" t="n">
-        <v>1545.111</v>
+        <v>1359.1542</v>
       </c>
       <c r="D4" t="n">
-        <v>1094.8088</v>
+        <v>977.9597</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B5" t="n">
-        <v>2622.687</v>
+        <v>2453.9192</v>
       </c>
       <c r="C5" t="n">
-        <v>1452.1326</v>
+        <v>1358.6889</v>
       </c>
       <c r="D5" t="n">
-        <v>1036.3843</v>
+        <v>1087.71</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B6" t="n">
-        <v>2454.7594</v>
+        <v>2609.1098</v>
       </c>
       <c r="C6" t="n">
-        <v>1359.1542</v>
+        <v>1487.4203</v>
       </c>
       <c r="D6" t="n">
-        <v>977.9597</v>
+        <v>1301.0027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="B7" t="n">
-        <v>2454.5914</v>
+        <v>3270.2215</v>
       </c>
       <c r="C7" t="n">
-        <v>1359.0612</v>
+        <v>1779.154</v>
       </c>
       <c r="D7" t="n">
-        <v>999.9098</v>
+        <v>1464.3113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B8" t="n">
-        <v>2454.4233</v>
+        <v>2750.7914</v>
       </c>
       <c r="C8" t="n">
-        <v>1358.9681</v>
+        <v>2291.6861</v>
       </c>
       <c r="D8" t="n">
-        <v>1021.8598</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>71</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2454.2552</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1358.8751</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1043.8099</v>
+        <v>1691.8236</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
-        <v>72</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2454.0872</v>
-      </c>
-      <c r="C10" t="n">
-        <v>1358.782</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1065.7599</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Claim-cost differentials</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
-        <v>73</v>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Male claim cost higher than female by</t>
+        </is>
       </c>
       <c r="B11" t="n">
-        <v>2453.9192</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1358.6889</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1087.71</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
-        <v>74</v>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Non-preferred higher than preferred by</t>
+        </is>
       </c>
       <c r="B12" t="n">
-        <v>2492.7168</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1390.8718</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1141.0332</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
-        <v>75</v>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Non-HHD higher than HHD by</t>
+        </is>
       </c>
       <c r="B13" t="n">
-        <v>2531.5144</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1423.0547</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1194.3563</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>76</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2570.3121</v>
-      </c>
-      <c r="C14" t="n">
-        <v>1455.2375</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1247.6795</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
-        <v>77</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2609.1098</v>
-      </c>
-      <c r="C15" t="n">
-        <v>1487.4203</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1301.0027</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Projection trend &amp; claim-cost aging by duration</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
-        <v>78</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2647.9075</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1519.6032</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1354.3259</v>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CC aging</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="B17" t="n">
-        <v>2772.3703</v>
+        <v>0.1</v>
       </c>
       <c r="C17" t="n">
-        <v>1571.5133</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1376.323</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>2896.8331</v>
+        <v>0.09</v>
       </c>
       <c r="C18" t="n">
-        <v>1623.4235</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1398.3201</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>81</v>
+        <v>3</v>
       </c>
       <c r="B19" t="n">
-        <v>3021.2959</v>
+        <v>0.08</v>
       </c>
       <c r="C19" t="n">
-        <v>1675.3337</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1420.3171</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>82</v>
+        <v>4</v>
       </c>
       <c r="B20" t="n">
-        <v>3145.7588</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>1727.2438</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1442.3142</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>83</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>3270.2215</v>
+        <v>0.06</v>
       </c>
       <c r="C21" t="n">
-        <v>1779.154</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1464.3113</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
-        <v>3010.5065</v>
+        <v>0.06</v>
       </c>
       <c r="C22" t="n">
-        <v>2181.3885</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1643.6096</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="B23" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C23" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1691.8236</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="B24" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C24" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1691.8236</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>87</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C25" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="B26" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C26" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="B27" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C27" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B28" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C28" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="B29" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C29" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="B30" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C30" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>93</v>
+        <v>15</v>
       </c>
       <c r="B31" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C31" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>94</v>
+        <v>16</v>
       </c>
       <c r="B32" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C32" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="B33" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C33" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="B34" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C34" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>97</v>
+        <v>19</v>
       </c>
       <c r="B35" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C35" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
       <c r="B36" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C36" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="B37" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C37" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="B38" t="n">
-        <v>2750.7914</v>
+        <v>0.06</v>
       </c>
       <c r="C38" t="n">
-        <v>2291.6861</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1691.8236</v>
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>23</v>
+      </c>
+      <c r="B39" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Claim-cost differentials</t>
-        </is>
+      <c r="A40" t="n">
+        <v>24</v>
+      </c>
+      <c r="B40" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Male claim cost higher than female by</t>
-        </is>
+      <c r="A41" t="n">
+        <v>25</v>
       </c>
       <c r="B41" t="n">
-        <v>0.15</v>
+        <v>0.06</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Non-preferred higher than preferred by</t>
-        </is>
+      <c r="A42" t="n">
+        <v>26</v>
       </c>
       <c r="B42" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Non-HHD higher than HHD by</t>
-        </is>
+      <c r="A43" t="n">
+        <v>27</v>
       </c>
       <c r="B43" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>28</v>
+      </c>
+      <c r="B44" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>Projection trend &amp; claim-cost aging by duration</t>
-        </is>
+      <c r="A45" t="n">
+        <v>29</v>
+      </c>
+      <c r="B45" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.015</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>Duration</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>CC aging</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="A46" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>State morbidity factors</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
         <v>1</v>
       </c>
-      <c r="B47" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.89612837</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>UW selection factors</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>issue_age</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>uw</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>1</v>
+      </c>
+      <c r="B81" t="n">
+        <v>65</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
         <v>2</v>
       </c>
-      <c r="B48" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C48" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="B82" t="n">
+        <v>65</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
         <v>3</v>
       </c>
-      <c r="B49" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C49" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="B83" t="n">
+        <v>65</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>4</v>
       </c>
-      <c r="B50" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="C50" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
+      <c r="B84" t="n">
+        <v>65</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
         <v>5</v>
       </c>
-      <c r="B51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C51" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>6</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C52" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>7</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>8</v>
-      </c>
-      <c r="B54" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C54" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>9</v>
-      </c>
-      <c r="B55" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C55" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>10</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C56" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>11</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C57" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>12</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>13</v>
-      </c>
-      <c r="B59" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C59" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>14</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C60" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>15</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>16</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C62" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>17</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C63" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>18</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C64" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>19</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>20</v>
-      </c>
-      <c r="B66" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>21</v>
-      </c>
-      <c r="B67" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C67" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>22</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C68" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>23</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C69" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>24</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C70" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>25</v>
-      </c>
-      <c r="B71" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>26</v>
-      </c>
-      <c r="B72" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C72" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>27</v>
-      </c>
-      <c r="B73" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C73" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>28</v>
-      </c>
-      <c r="B74" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C74" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>29</v>
-      </c>
-      <c r="B75" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>30</v>
-      </c>
-      <c r="B76" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C76" t="n">
-        <v>0.015</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="inlineStr">
-        <is>
-          <t>State morbidity factors</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>Factor</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
+      <c r="B85" t="n">
+        <v>65</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>OE</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.89612837</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>state</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="inlineStr">
-        <is>
-          <t>UW selection factors</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>issue_age</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>uw</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>factor</t>
-        </is>
       </c>
     </row>
     <row r="86">
@@ -2056,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="B86" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -2064,7 +1977,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="87">
@@ -2072,7 +1985,7 @@
         <v>2</v>
       </c>
       <c r="B87" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -2080,7 +1993,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="88">
@@ -2088,7 +2001,7 @@
         <v>3</v>
       </c>
       <c r="B88" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -2096,7 +2009,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="89">
@@ -2104,7 +2017,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -2112,7 +2025,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="90">
@@ -2120,7 +2033,7 @@
         <v>5</v>
       </c>
       <c r="B90" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -2128,7 +2041,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>1.035</v>
       </c>
     </row>
     <row r="91">
@@ -2136,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="B91" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -2144,7 +2057,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1.035</v>
+        <v>1.325</v>
       </c>
     </row>
     <row r="92">
@@ -2152,7 +2065,7 @@
         <v>2</v>
       </c>
       <c r="B92" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -2160,7 +2073,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1.035</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="93">
@@ -2168,7 +2081,7 @@
         <v>3</v>
       </c>
       <c r="B93" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -2176,7 +2089,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1.035</v>
+        <v>1.275</v>
       </c>
     </row>
     <row r="94">
@@ -2184,7 +2097,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -2192,7 +2105,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1.035</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="95">
@@ -2200,7 +2113,7 @@
         <v>5</v>
       </c>
       <c r="B95" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -2208,7 +2121,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1.035</v>
+        <v>1.225</v>
       </c>
     </row>
     <row r="96">
@@ -2216,7 +2129,7 @@
         <v>1</v>
       </c>
       <c r="B96" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -2224,7 +2137,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1.325</v>
+        <v>1.525</v>
       </c>
     </row>
     <row r="97">
@@ -2232,7 +2145,7 @@
         <v>2</v>
       </c>
       <c r="B97" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -2240,7 +2153,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="98">
@@ -2248,7 +2161,7 @@
         <v>3</v>
       </c>
       <c r="B98" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -2256,7 +2169,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1.275</v>
+        <v>1.475</v>
       </c>
     </row>
     <row r="99">
@@ -2264,7 +2177,7 @@
         <v>4</v>
       </c>
       <c r="B99" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -2272,7 +2185,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="100">
@@ -2280,7 +2193,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -2288,7 +2201,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1.225</v>
+        <v>1.425</v>
       </c>
     </row>
     <row r="101">
@@ -2296,7 +2209,7 @@
         <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -2304,7 +2217,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1.525</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -2312,7 +2225,7 @@
         <v>2</v>
       </c>
       <c r="B102" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -2320,7 +2233,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1.5</v>
+        <v>1.975</v>
       </c>
     </row>
     <row r="103">
@@ -2328,7 +2241,7 @@
         <v>3</v>
       </c>
       <c r="B103" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -2336,7 +2249,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1.475</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="104">
@@ -2344,7 +2257,7 @@
         <v>4</v>
       </c>
       <c r="B104" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -2352,7 +2265,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1.45</v>
+        <v>1.925</v>
       </c>
     </row>
     <row r="105">
@@ -2360,7 +2273,7 @@
         <v>5</v>
       </c>
       <c r="B105" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -2368,7 +2281,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1.425</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="106">
@@ -2376,7 +2289,7 @@
         <v>1</v>
       </c>
       <c r="B106" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -2392,7 +2305,7 @@
         <v>2</v>
       </c>
       <c r="B107" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -2408,7 +2321,7 @@
         <v>3</v>
       </c>
       <c r="B108" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -2424,7 +2337,7 @@
         <v>4</v>
       </c>
       <c r="B109" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -2440,7 +2353,7 @@
         <v>5</v>
       </c>
       <c r="B110" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -2456,15 +2369,15 @@
         <v>1</v>
       </c>
       <c r="B111" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="112">
@@ -2472,15 +2385,15 @@
         <v>2</v>
       </c>
       <c r="B112" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.975</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="113">
@@ -2488,15 +2401,15 @@
         <v>3</v>
       </c>
       <c r="B113" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1.95</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="114">
@@ -2504,15 +2417,15 @@
         <v>4</v>
       </c>
       <c r="B114" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1.925</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="115">
@@ -2520,15 +2433,15 @@
         <v>5</v>
       </c>
       <c r="B115" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>OE</t>
+          <t>GI</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1.9</v>
+        <v>2.175</v>
       </c>
     </row>
     <row r="116">
@@ -2536,7 +2449,7 @@
         <v>1</v>
       </c>
       <c r="B116" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -2544,7 +2457,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>2.175</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="117">
@@ -2552,7 +2465,7 @@
         <v>2</v>
       </c>
       <c r="B117" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -2560,7 +2473,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>2.175</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="118">
@@ -2568,7 +2481,7 @@
         <v>3</v>
       </c>
       <c r="B118" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -2576,7 +2489,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>2.175</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="119">
@@ -2584,7 +2497,7 @@
         <v>4</v>
       </c>
       <c r="B119" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -2592,7 +2505,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2.175</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="120">
@@ -2600,7 +2513,7 @@
         <v>5</v>
       </c>
       <c r="B120" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -2608,7 +2521,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>2.175</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="121">
@@ -2616,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="B121" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -2632,7 +2545,7 @@
         <v>2</v>
       </c>
       <c r="B122" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -2648,7 +2561,7 @@
         <v>3</v>
       </c>
       <c r="B123" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -2664,7 +2577,7 @@
         <v>4</v>
       </c>
       <c r="B124" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -2680,7 +2593,7 @@
         <v>5</v>
       </c>
       <c r="B125" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -2696,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="B126" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -2712,7 +2625,7 @@
         <v>2</v>
       </c>
       <c r="B127" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -2728,7 +2641,7 @@
         <v>3</v>
       </c>
       <c r="B128" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -2744,7 +2657,7 @@
         <v>4</v>
       </c>
       <c r="B129" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -2760,7 +2673,7 @@
         <v>5</v>
       </c>
       <c r="B130" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -2776,7 +2689,7 @@
         <v>1</v>
       </c>
       <c r="B131" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -2792,7 +2705,7 @@
         <v>2</v>
       </c>
       <c r="B132" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -2808,7 +2721,7 @@
         <v>3</v>
       </c>
       <c r="B133" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -2824,7 +2737,7 @@
         <v>4</v>
       </c>
       <c r="B134" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -2840,7 +2753,7 @@
         <v>5</v>
       </c>
       <c r="B135" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -2856,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="B136" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -2872,7 +2785,7 @@
         <v>2</v>
       </c>
       <c r="B137" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -2888,7 +2801,7 @@
         <v>3</v>
       </c>
       <c r="B138" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -2904,7 +2817,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -2920,7 +2833,7 @@
         <v>5</v>
       </c>
       <c r="B140" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -2936,15 +2849,15 @@
         <v>1</v>
       </c>
       <c r="B141" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>2.5</v>
+        <v>0.475</v>
       </c>
     </row>
     <row r="142">
@@ -2952,15 +2865,15 @@
         <v>2</v>
       </c>
       <c r="B142" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="143">
@@ -2968,15 +2881,15 @@
         <v>3</v>
       </c>
       <c r="B143" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>2.5</v>
+        <v>0.525</v>
       </c>
     </row>
     <row r="144">
@@ -2984,15 +2897,15 @@
         <v>4</v>
       </c>
       <c r="B144" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>2.5</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="145">
@@ -3000,15 +2913,15 @@
         <v>5</v>
       </c>
       <c r="B145" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>GI</t>
+          <t>UW</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2.5</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="146">
@@ -3016,7 +2929,7 @@
         <v>1</v>
       </c>
       <c r="B146" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -3024,7 +2937,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>0.475</v>
+        <v>0.575</v>
       </c>
     </row>
     <row r="147">
@@ -3032,7 +2945,7 @@
         <v>2</v>
       </c>
       <c r="B147" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -3040,7 +2953,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="148">
@@ -3048,7 +2961,7 @@
         <v>3</v>
       </c>
       <c r="B148" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -3056,7 +2969,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>0.525</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="149">
@@ -3064,7 +2977,7 @@
         <v>4</v>
       </c>
       <c r="B149" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -3072,7 +2985,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="150">
@@ -3080,7 +2993,7 @@
         <v>5</v>
       </c>
       <c r="B150" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -3088,7 +3001,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>0.575</v>
+        <v>0.675</v>
       </c>
     </row>
     <row r="151">
@@ -3096,7 +3009,7 @@
         <v>1</v>
       </c>
       <c r="B151" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -3104,7 +3017,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>0.575</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="152">
@@ -3112,7 +3025,7 @@
         <v>2</v>
       </c>
       <c r="B152" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -3120,7 +3033,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>0.6</v>
+        <v>0.825</v>
       </c>
     </row>
     <row r="153">
@@ -3128,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="B153" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -3136,7 +3049,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>0.625</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="154">
@@ -3144,7 +3057,7 @@
         <v>4</v>
       </c>
       <c r="B154" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -3152,7 +3065,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>0.65</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="155">
@@ -3160,7 +3073,7 @@
         <v>5</v>
       </c>
       <c r="B155" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -3168,7 +3081,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>0.675</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="156">
@@ -3176,7 +3089,7 @@
         <v>1</v>
       </c>
       <c r="B156" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -3192,7 +3105,7 @@
         <v>2</v>
       </c>
       <c r="B157" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -3208,7 +3121,7 @@
         <v>3</v>
       </c>
       <c r="B158" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -3224,7 +3137,7 @@
         <v>4</v>
       </c>
       <c r="B159" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -3240,7 +3153,7 @@
         <v>5</v>
       </c>
       <c r="B160" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -3256,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="B161" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -3272,7 +3185,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -3288,7 +3201,7 @@
         <v>3</v>
       </c>
       <c r="B163" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -3304,7 +3217,7 @@
         <v>4</v>
       </c>
       <c r="B164" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -3320,7 +3233,7 @@
         <v>5</v>
       </c>
       <c r="B165" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -3336,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="B166" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -3344,7 +3257,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>0.8</v>
+        <v>0.875</v>
       </c>
     </row>
     <row r="167">
@@ -3352,7 +3265,7 @@
         <v>2</v>
       </c>
       <c r="B167" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -3360,7 +3273,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>0.825</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="168">
@@ -3368,7 +3281,7 @@
         <v>3</v>
       </c>
       <c r="B168" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -3376,7 +3289,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>0.85</v>
+        <v>0.925</v>
       </c>
     </row>
     <row r="169">
@@ -3384,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="B169" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -3392,7 +3305,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>0.875</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="170">
@@ -3400,7 +3313,7 @@
         <v>5</v>
       </c>
       <c r="B170" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -3408,86 +3321,6 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="n">
-        <v>1</v>
-      </c>
-      <c r="B171" t="n">
-        <v>85</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>UW</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="n">
-        <v>2</v>
-      </c>
-      <c r="B172" t="n">
-        <v>85</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>UW</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="n">
-        <v>3</v>
-      </c>
-      <c r="B173" t="n">
-        <v>85</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>UW</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>0.925</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="n">
-        <v>4</v>
-      </c>
-      <c r="B174" t="n">
-        <v>85</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>UW</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="n">
-        <v>5</v>
-      </c>
-      <c r="B175" t="n">
-        <v>85</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>UW</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
         <v>0.975</v>
       </c>
     </row>
@@ -3502,7 +3335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B34"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3733,17 +3566,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0.997529</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>All</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -3753,41 +3586,261 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.040706</v>
+        <v>1.444136</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.343158</v>
+        <v>1.243395</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.040706</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1.040706</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1.015832</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.202572</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1.141699</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1.031789</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1.214861</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1.343158</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1.342756</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1.203929</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.91556</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1.868104</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.84861</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1.400928</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1.400999</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1.135502</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1.005004</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1.101135</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.952847</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1.040706</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B53" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1.124967</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1.198471</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1.203032</v>
       </c>
     </row>
   </sheetData>
@@ -4993,7 +5046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5403,7 +5456,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -5413,837 +5466,1097 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>All</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="43">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
         <is>
           <t>Mortality table</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Age</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>qx</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>0</v>
-      </c>
-      <c r="B45" t="n">
-        <v>0.005777</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" t="n">
-        <v>0.000382</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2</v>
-      </c>
-      <c r="B47" t="n">
-        <v>0.000248</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B48" t="n">
-        <v>0.000193</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" t="n">
-        <v>0.000149</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>5</v>
-      </c>
-      <c r="B50" t="n">
-        <v>0.000141</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>6</v>
-      </c>
-      <c r="B51" t="n">
-        <v>0.000126</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>7</v>
-      </c>
-      <c r="B52" t="n">
-        <v>0.000114</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>8</v>
-      </c>
-      <c r="B53" t="n">
-        <v>0.000104</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>9</v>
-      </c>
-      <c r="B54" t="n">
-        <v>9.500000000000001e-05</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>10</v>
-      </c>
-      <c r="B55" t="n">
-        <v>9.3e-05</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>11</v>
-      </c>
-      <c r="B56" t="n">
-        <v>0.000103</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>12</v>
-      </c>
-      <c r="B57" t="n">
-        <v>0.000133</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>13</v>
-      </c>
-      <c r="B58" t="n">
-        <v>0.000186</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>14</v>
-      </c>
-      <c r="B59" t="n">
-        <v>0.000258</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>15</v>
-      </c>
-      <c r="B60" t="n">
-        <v>0.000338</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>16</v>
-      </c>
-      <c r="B61" t="n">
-        <v>0.000421</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>17</v>
-      </c>
-      <c r="B62" t="n">
-        <v>0.00051</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>18</v>
-      </c>
-      <c r="B63" t="n">
-        <v>0.000603</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>19</v>
-      </c>
-      <c r="B64" t="n">
-        <v>0.0006980000000000001</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>20</v>
-      </c>
-      <c r="B65" t="n">
-        <v>0.000795</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>21</v>
-      </c>
-      <c r="B66" t="n">
-        <v>0.000889</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>22</v>
-      </c>
-      <c r="B67" t="n">
-        <v>0.0009700000000000001</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>23</v>
-      </c>
-      <c r="B68" t="n">
-        <v>0.001032</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>24</v>
-      </c>
-      <c r="B69" t="n">
-        <v>0.00108</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>25</v>
-      </c>
-      <c r="B70" t="n">
-        <v>0.001123</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="B71" t="n">
-        <v>0.001165</v>
+        <v>0.005777</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="B72" t="n">
-        <v>0.001207</v>
+        <v>0.000382</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B73" t="n">
-        <v>0.001252</v>
+        <v>0.000248</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0013</v>
+        <v>0.000193</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B75" t="n">
-        <v>0.001351</v>
+        <v>0.000149</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B76" t="n">
-        <v>0.001402</v>
+        <v>0.000141</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B77" t="n">
-        <v>0.001454</v>
+        <v>0.000126</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B78" t="n">
-        <v>0.001506</v>
+        <v>0.000114</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B79" t="n">
-        <v>0.001556</v>
+        <v>0.000104</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B80" t="n">
-        <v>0.001615</v>
+        <v>9.500000000000001e-05</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B81" t="n">
-        <v>0.001679</v>
+        <v>9.3e-05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="B82" t="n">
-        <v>0.00174</v>
+        <v>0.000103</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B83" t="n">
-        <v>0.001798</v>
+        <v>0.000133</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B84" t="n">
-        <v>0.00186</v>
+        <v>0.000186</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="B85" t="n">
-        <v>0.001936</v>
+        <v>0.000258</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B86" t="n">
-        <v>0.002036</v>
+        <v>0.000338</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B87" t="n">
-        <v>0.00216</v>
+        <v>0.000421</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B88" t="n">
-        <v>0.002306</v>
+        <v>0.00051</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B89" t="n">
-        <v>0.00247</v>
+        <v>0.000603</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B90" t="n">
-        <v>0.002647</v>
+        <v>0.0006980000000000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B91" t="n">
-        <v>0.002846</v>
+        <v>0.000795</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="B92" t="n">
-        <v>0.003079</v>
+        <v>0.000889</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="B93" t="n">
-        <v>0.003357</v>
+        <v>0.0009700000000000001</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="B94" t="n">
-        <v>0.003682</v>
+        <v>0.001032</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="B95" t="n">
-        <v>0.00403</v>
+        <v>0.00108</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="B96" t="n">
-        <v>0.004401</v>
+        <v>0.001123</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B97" t="n">
-        <v>0.00482</v>
+        <v>0.001165</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="B98" t="n">
-        <v>0.005285</v>
+        <v>0.001207</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="B99" t="n">
-        <v>0.005778</v>
+        <v>0.001252</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="B100" t="n">
-        <v>0.006284</v>
+        <v>0.0013</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="B101" t="n">
-        <v>0.006794</v>
+        <v>0.001351</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="B102" t="n">
-        <v>0.007319</v>
+        <v>0.001402</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="B103" t="n">
-        <v>0.007868999999999999</v>
+        <v>0.001454</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="B104" t="n">
-        <v>0.008456</v>
+        <v>0.001506</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="B105" t="n">
-        <v>0.009093</v>
+        <v>0.001556</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="B106" t="n">
-        <v>0.009768000000000001</v>
+        <v>0.001615</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="B107" t="n">
-        <v>0.010467</v>
+        <v>0.001679</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="B108" t="n">
-        <v>0.011181</v>
+        <v>0.00174</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B109" t="n">
-        <v>0.011922</v>
+        <v>0.001798</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="B110" t="n">
-        <v>0.01271</v>
+        <v>0.00186</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="B111" t="n">
-        <v>0.013621</v>
+        <v>0.001936</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="B112" t="n">
-        <v>0.01462</v>
+        <v>0.002036</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="B113" t="n">
-        <v>0.01577</v>
+        <v>0.00216</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0171</v>
+        <v>0.002306</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="B115" t="n">
-        <v>0.018428</v>
+        <v>0.00247</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="B116" t="n">
-        <v>0.020317</v>
+        <v>0.002647</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="B117" t="n">
-        <v>0.022102</v>
+        <v>0.002846</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="B118" t="n">
-        <v>0.024194</v>
+        <v>0.003079</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B119" t="n">
-        <v>0.026342</v>
+        <v>0.003357</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="B120" t="n">
-        <v>0.029042</v>
+        <v>0.003682</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="B121" t="n">
-        <v>0.032001</v>
+        <v>0.00403</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="B122" t="n">
-        <v>0.035443</v>
+        <v>0.004401</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="B123" t="n">
-        <v>0.039257</v>
+        <v>0.00482</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="B124" t="n">
-        <v>0.043393</v>
+        <v>0.005285</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="B125" t="n">
-        <v>0.048163</v>
+        <v>0.005778</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="B126" t="n">
-        <v>0.053216</v>
+        <v>0.006284</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B127" t="n">
-        <v>0.05924</v>
+        <v>0.006794</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="B128" t="n">
-        <v>0.066564</v>
+        <v>0.007319</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="B129" t="n">
-        <v>0.074045</v>
+        <v>0.007868999999999999</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="B130" t="n">
-        <v>0.081954</v>
+        <v>0.008456</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="B131" t="n">
-        <v>0.090879</v>
+        <v>0.009093</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="B132" t="n">
-        <v>0.101938</v>
+        <v>0.009768000000000001</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>88</v>
+        <v>62</v>
       </c>
       <c r="B133" t="n">
-        <v>0.114075</v>
+        <v>0.010467</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="B134" t="n">
-        <v>0.127331</v>
+        <v>0.011181</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="B135" t="n">
-        <v>0.141733</v>
+        <v>0.011922</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="B136" t="n">
-        <v>0.157289</v>
+        <v>0.01271</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="B137" t="n">
-        <v>0.173986</v>
+        <v>0.013621</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="B138" t="n">
-        <v>0.191788</v>
+        <v>0.01462</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>94</v>
+        <v>68</v>
       </c>
       <c r="B139" t="n">
-        <v>0.210633</v>
+        <v>0.01577</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="B140" t="n">
-        <v>0.230432</v>
+        <v>0.0171</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="B141" t="n">
-        <v>0.251066</v>
+        <v>0.018428</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B142" t="n">
-        <v>0.272395</v>
+        <v>0.020317</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="B143" t="n">
-        <v>0.294253</v>
+        <v>0.022102</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>99</v>
+        <v>73</v>
       </c>
       <c r="B144" t="n">
-        <v>0.316456</v>
+        <v>0.024194</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
+        <v>74</v>
+      </c>
+      <c r="B145" t="n">
+        <v>0.026342</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>75</v>
+      </c>
+      <c r="B146" t="n">
+        <v>0.029042</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>76</v>
+      </c>
+      <c r="B147" t="n">
+        <v>0.032001</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>77</v>
+      </c>
+      <c r="B148" t="n">
+        <v>0.035443</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>78</v>
+      </c>
+      <c r="B149" t="n">
+        <v>0.039257</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>79</v>
+      </c>
+      <c r="B150" t="n">
+        <v>0.043393</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>80</v>
+      </c>
+      <c r="B151" t="n">
+        <v>0.048163</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>81</v>
+      </c>
+      <c r="B152" t="n">
+        <v>0.053216</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>82</v>
+      </c>
+      <c r="B153" t="n">
+        <v>0.05924</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>83</v>
+      </c>
+      <c r="B154" t="n">
+        <v>0.066564</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>84</v>
+      </c>
+      <c r="B155" t="n">
+        <v>0.074045</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>85</v>
+      </c>
+      <c r="B156" t="n">
+        <v>0.081954</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>86</v>
+      </c>
+      <c r="B157" t="n">
+        <v>0.090879</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>87</v>
+      </c>
+      <c r="B158" t="n">
+        <v>0.101938</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>88</v>
+      </c>
+      <c r="B159" t="n">
+        <v>0.114075</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>89</v>
+      </c>
+      <c r="B160" t="n">
+        <v>0.127331</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>90</v>
+      </c>
+      <c r="B161" t="n">
+        <v>0.141733</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>91</v>
+      </c>
+      <c r="B162" t="n">
+        <v>0.157289</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>92</v>
+      </c>
+      <c r="B163" t="n">
+        <v>0.173986</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>93</v>
+      </c>
+      <c r="B164" t="n">
+        <v>0.191788</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>94</v>
+      </c>
+      <c r="B165" t="n">
+        <v>0.210633</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>95</v>
+      </c>
+      <c r="B166" t="n">
+        <v>0.230432</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>96</v>
+      </c>
+      <c r="B167" t="n">
+        <v>0.251066</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>97</v>
+      </c>
+      <c r="B168" t="n">
+        <v>0.272395</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>98</v>
+      </c>
+      <c r="B169" t="n">
+        <v>0.294253</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>99</v>
+      </c>
+      <c r="B170" t="n">
+        <v>0.316456</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
         <v>100</v>
       </c>
-      <c r="B145" t="n">
+      <c r="B171" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6258,7 +6571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6285,7 +6598,137 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>TX</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>MD</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>WI</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>FL</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>OH</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>KS</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>NH</t>
         </is>
       </c>
     </row>
@@ -6297,6 +6740,84 @@
         <v>0.261</v>
       </c>
       <c r="C3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC3" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -6308,6 +6829,84 @@
         <v>0.261</v>
       </c>
       <c r="C4" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC4" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -6319,6 +6918,84 @@
         <v>0.261</v>
       </c>
       <c r="C5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC5" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -6330,6 +7007,84 @@
         <v>0.261</v>
       </c>
       <c r="C6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC6" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -6341,6 +7096,84 @@
         <v>0.261</v>
       </c>
       <c r="C7" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC7" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -6352,6 +7185,84 @@
         <v>0.261</v>
       </c>
       <c r="C8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="AC8" t="n">
         <v>0.261</v>
       </c>
     </row>
@@ -6363,6 +7274,84 @@
         <v>0.09</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC9" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6374,6 +7363,84 @@
         <v>0.09</v>
       </c>
       <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC10" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6385,6 +7452,84 @@
         <v>0.09</v>
       </c>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC11" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6396,6 +7541,84 @@
         <v>0.09</v>
       </c>
       <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AC12" t="n">
         <v>0.09</v>
       </c>
     </row>
@@ -6407,6 +7630,84 @@
         <v>0.018</v>
       </c>
       <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC13" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6418,6 +7719,84 @@
         <v>0.018</v>
       </c>
       <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC14" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6429,6 +7808,84 @@
         <v>0.018</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC15" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6440,6 +7897,84 @@
         <v>0.018</v>
       </c>
       <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC16" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6451,6 +7986,84 @@
         <v>0.018</v>
       </c>
       <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC17" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6462,6 +8075,84 @@
         <v>0.018</v>
       </c>
       <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC18" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6473,6 +8164,84 @@
         <v>0.018</v>
       </c>
       <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC19" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6484,6 +8253,84 @@
         <v>0.018</v>
       </c>
       <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC20" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6495,6 +8342,84 @@
         <v>0.018</v>
       </c>
       <c r="C21" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC21" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6506,6 +8431,84 @@
         <v>0.018</v>
       </c>
       <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC22" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6517,6 +8520,84 @@
         <v>0.018</v>
       </c>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC23" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6528,6 +8609,84 @@
         <v>0.018</v>
       </c>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC24" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6539,6 +8698,84 @@
         <v>0.018</v>
       </c>
       <c r="C25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC25" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6550,6 +8787,84 @@
         <v>0.018</v>
       </c>
       <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC26" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6561,6 +8876,84 @@
         <v>0.018</v>
       </c>
       <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC27" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6572,6 +8965,84 @@
         <v>0.018</v>
       </c>
       <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC28" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6583,6 +9054,84 @@
         <v>0.018</v>
       </c>
       <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC29" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6594,6 +9143,84 @@
         <v>0.018</v>
       </c>
       <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC30" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6605,6 +9232,84 @@
         <v>0.018</v>
       </c>
       <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC31" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -6616,6 +9321,84 @@
         <v>0.018</v>
       </c>
       <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AC32" t="n">
         <v>0.018</v>
       </c>
     </row>
